--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2024.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Migración interna neta</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2024.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:21</t>
+    <t xml:space="preserve">2026-07-30 15:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_miginterna_a_2024.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Migracion interna neta</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2024</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2024.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">Aysen</t>
@@ -541,18 +541,18 @@
     <t xml:space="preserve">Lampa</t>
   </si>
   <si>
+    <t xml:space="preserve">5501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
     <t xml:space="preserve">7304</t>
   </si>
   <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">5501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
     <t xml:space="preserve">16106</t>
   </si>
   <si>
@@ -589,18 +589,18 @@
     <t xml:space="preserve">Quintero</t>
   </si>
   <si>
+    <t xml:space="preserve">13132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
     <t xml:space="preserve">7404</t>
   </si>
   <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
-    <t xml:space="preserve">13132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
     <t xml:space="preserve">6113</t>
   </si>
   <si>
@@ -763,18 +763,18 @@
     <t xml:space="preserve">Coinco</t>
   </si>
   <si>
+    <t xml:space="preserve">6107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
     <t xml:space="preserve">16201</t>
   </si>
   <si>
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
-    <t xml:space="preserve">6107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Cabras</t>
-  </si>
-  <si>
     <t xml:space="preserve">13501</t>
   </si>
   <si>
@@ -847,18 +847,18 @@
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">6310</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
-    <t xml:space="preserve">5702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">13129</t>
   </si>
   <si>
@@ -973,18 +973,18 @@
     <t xml:space="preserve">Malloa</t>
   </si>
   <si>
+    <t xml:space="preserve">5301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
     <t xml:space="preserve">13126</t>
   </si>
   <si>
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">5301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
     <t xml:space="preserve">7202</t>
   </si>
   <si>
@@ -1045,18 +1045,18 @@
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
+    <t xml:space="preserve">5302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
     <t xml:space="preserve">13118</t>
   </si>
   <si>
     <t xml:space="preserve">Macul</t>
   </si>
   <si>
-    <t xml:space="preserve">5302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
     <t xml:space="preserve">6301</t>
   </si>
   <si>
@@ -1726,18 +1726,18 @@
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
+    <t xml:space="preserve">14103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
     <t xml:space="preserve">10304</t>
   </si>
   <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
-    <t xml:space="preserve">14103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">14204</t>
   </si>
   <si>
@@ -1810,18 +1810,18 @@
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
+    <t xml:space="preserve">8111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
     <t xml:space="preserve">10108</t>
   </si>
   <si>
     <t xml:space="preserve">Maullín</t>
   </si>
   <si>
-    <t xml:space="preserve">8111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
     <t xml:space="preserve">9203</t>
   </si>
   <si>
@@ -1900,34 +1900,40 @@
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
+    <t xml:space="preserve">9201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angol</t>
+  </si>
+  <si>
     <t xml:space="preserve">10207</t>
   </si>
   <si>
     <t xml:space="preserve">Queilén</t>
   </si>
   <si>
-    <t xml:space="preserve">9201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angol</t>
-  </si>
-  <si>
     <t xml:space="preserve">8202</t>
   </si>
   <si>
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
+    <t xml:space="preserve">9113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perquenco</t>
+  </si>
+  <si>
     <t xml:space="preserve">10104</t>
   </si>
   <si>
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
-    <t xml:space="preserve">9113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perquenco</t>
+    <t xml:space="preserve">8109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
     <t xml:space="preserve">10210</t>
@@ -1936,12 +1942,6 @@
     <t xml:space="preserve">Quinchao</t>
   </si>
   <si>
-    <t xml:space="preserve">8109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
-  </si>
-  <si>
     <t xml:space="preserve">14201</t>
   </si>
   <si>
@@ -1978,18 +1978,18 @@
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
+    <t xml:space="preserve">9119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilcún</t>
+  </si>
+  <si>
     <t xml:space="preserve">10102</t>
   </si>
   <si>
     <t xml:space="preserve">Calbuco</t>
   </si>
   <si>
-    <t xml:space="preserve">9119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vilcún</t>
-  </si>
-  <si>
     <t xml:space="preserve">10202</t>
   </si>
   <si>
@@ -2020,33 +2020,33 @@
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
+    <t xml:space="preserve">14104</t>
+  </si>
+  <si>
     <t xml:space="preserve">10301</t>
   </si>
   <si>
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
-    <t xml:space="preserve">14104</t>
-  </si>
-  <si>
     <t xml:space="preserve">10208</t>
   </si>
   <si>
     <t xml:space="preserve">Quellón</t>
   </si>
   <si>
+    <t xml:space="preserve">8107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
     <t xml:space="preserve">9209</t>
   </si>
   <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
-    <t xml:space="preserve">8107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
     <t xml:space="preserve">9111</t>
   </si>
   <si>
@@ -2089,18 +2089,18 @@
     <t xml:space="preserve">Los Angeles</t>
   </si>
   <si>
+    <t xml:space="preserve">8205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">10303</t>
   </si>
   <si>
     <t xml:space="preserve">Purranque</t>
   </si>
   <si>
-    <t xml:space="preserve">8205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">9103</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:29</t>
+    <t xml:space="preserve">2026-09-08 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5096,10 +5096,10 @@
         <v>2024</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>174</v>
@@ -5128,10 +5128,10 @@
         <v>2024</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>176</v>
@@ -5352,10 +5352,10 @@
         <v>2024</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>190</v>
@@ -5384,10 +5384,10 @@
         <v>2024</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>192</v>
@@ -6280,10 +6280,10 @@
         <v>2024</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>248</v>
@@ -6312,10 +6312,10 @@
         <v>2024</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>250</v>
@@ -6728,10 +6728,10 @@
         <v>2024</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>276</v>
@@ -6760,10 +6760,10 @@
         <v>2024</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>278</v>
@@ -7400,10 +7400,10 @@
         <v>2024</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>318</v>
@@ -7432,10 +7432,10 @@
         <v>2024</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>320</v>
@@ -7784,10 +7784,10 @@
         <v>2024</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>342</v>
@@ -7816,10 +7816,10 @@
         <v>2024</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>344</v>
@@ -11240,10 +11240,10 @@
         <v>2024</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>569</v>
@@ -11272,10 +11272,10 @@
         <v>2024</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>571</v>
@@ -11688,10 +11688,10 @@
         <v>2024</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>597</v>
@@ -11720,10 +11720,10 @@
         <v>2024</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>599</v>
@@ -12168,10 +12168,10 @@
         <v>2024</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>627</v>
@@ -12200,10 +12200,10 @@
         <v>2024</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>629</v>
@@ -12264,10 +12264,10 @@
         <v>2024</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>633</v>
@@ -12296,10 +12296,10 @@
         <v>2024</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>635</v>
@@ -12328,10 +12328,10 @@
         <v>2024</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>637</v>
@@ -12360,10 +12360,10 @@
         <v>2024</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>639</v>
@@ -12584,10 +12584,10 @@
         <v>2024</v>
       </c>
       <c r="B313" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>653</v>
@@ -12616,10 +12616,10 @@
         <v>2024</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>655</v>
@@ -12808,16 +12808,16 @@
         <v>2024</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>667</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>668</v>
+        <v>502</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>500</v>
@@ -12840,16 +12840,16 @@
         <v>2024</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="D321" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>500</v>
@@ -12904,10 +12904,10 @@
         <v>2024</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>672</v>
@@ -12936,10 +12936,10 @@
         <v>2024</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>674</v>
@@ -13192,10 +13192,10 @@
         <v>2024</v>
       </c>
       <c r="B332" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>690</v>
@@ -13224,10 +13224,10 @@
         <v>2024</v>
       </c>
       <c r="B333" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>692</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
